--- a/Proyecto Interno/food-security-paper/output/tables/table_income_summary.xlsx
+++ b/Proyecto Interno/food-security-paper/output/tables/table_income_summary.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -547,50 +547,50 @@
         <v>2023</v>
       </c>
       <c r="C7">
-        <v>2155699</v>
+        <v>2312956</v>
       </c>
       <c r="D7">
-        <v>3038656</v>
+        <v>3189610</v>
       </c>
       <c r="E7">
-        <v>1201923</v>
+        <v>1320833</v>
       </c>
       <c r="F7">
-        <v>331500</v>
+        <v>391389</v>
       </c>
       <c r="G7">
-        <v>4867917</v>
+        <v>5150000</v>
       </c>
       <c r="H7">
-        <v>2281</v>
+        <v>9322</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Cali</t>
+          <t>Bogotá</t>
         </is>
       </c>
       <c r="B8">
-        <v>2018</v>
+        <v>2024</v>
       </c>
       <c r="C8">
-        <v>1026439</v>
+        <v>2603861</v>
       </c>
       <c r="D8">
-        <v>1241529</v>
+        <v>3643506</v>
       </c>
       <c r="E8">
-        <v>687778</v>
+        <v>1512400</v>
       </c>
       <c r="F8">
-        <v>250000</v>
+        <v>484444</v>
       </c>
       <c r="G8">
-        <v>2029667</v>
+        <v>5735167</v>
       </c>
       <c r="H8">
-        <v>9421</v>
+        <v>9781</v>
       </c>
     </row>
     <row r="9">
@@ -600,25 +600,25 @@
         </is>
       </c>
       <c r="B9">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="C9">
-        <v>1101066</v>
+        <v>1026439</v>
       </c>
       <c r="D9">
-        <v>1395557</v>
+        <v>1241529</v>
       </c>
       <c r="E9">
-        <v>737500</v>
+        <v>687778</v>
       </c>
       <c r="F9">
         <v>250000</v>
       </c>
       <c r="G9">
-        <v>2144444</v>
+        <v>2029667</v>
       </c>
       <c r="H9">
-        <v>9589</v>
+        <v>9421</v>
       </c>
     </row>
     <row r="10">
@@ -628,25 +628,25 @@
         </is>
       </c>
       <c r="B10">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C10">
-        <v>952555</v>
+        <v>1101066</v>
       </c>
       <c r="D10">
-        <v>1363086</v>
+        <v>1395557</v>
       </c>
       <c r="E10">
-        <v>585000</v>
+        <v>737500</v>
       </c>
       <c r="F10">
-        <v>121667</v>
+        <v>250000</v>
       </c>
       <c r="G10">
-        <v>2006578</v>
+        <v>2144444</v>
       </c>
       <c r="H10">
-        <v>9161</v>
+        <v>9589</v>
       </c>
     </row>
     <row r="11">
@@ -656,25 +656,25 @@
         </is>
       </c>
       <c r="B11">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C11">
-        <v>1103852</v>
+        <v>952555</v>
       </c>
       <c r="D11">
-        <v>1547299</v>
+        <v>1363086</v>
       </c>
       <c r="E11">
-        <v>705750</v>
+        <v>585000</v>
       </c>
       <c r="F11">
-        <v>218667</v>
+        <v>121667</v>
       </c>
       <c r="G11">
-        <v>2254858</v>
+        <v>2006578</v>
       </c>
       <c r="H11">
-        <v>8910</v>
+        <v>9161</v>
       </c>
     </row>
     <row r="12">
@@ -684,25 +684,25 @@
         </is>
       </c>
       <c r="B12">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C12">
-        <v>1505300</v>
+        <v>1103852</v>
       </c>
       <c r="D12">
-        <v>2141240</v>
+        <v>1547299</v>
       </c>
       <c r="E12">
-        <v>900000</v>
+        <v>705750</v>
       </c>
       <c r="F12">
-        <v>296437</v>
+        <v>218667</v>
       </c>
       <c r="G12">
-        <v>3215101</v>
+        <v>2254858</v>
       </c>
       <c r="H12">
-        <v>11207</v>
+        <v>8910</v>
       </c>
     </row>
     <row r="13">
@@ -712,81 +712,81 @@
         </is>
       </c>
       <c r="B13">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C13">
-        <v>1586549</v>
+        <v>1505300</v>
       </c>
       <c r="D13">
-        <v>3285389</v>
+        <v>2141240</v>
       </c>
       <c r="E13">
-        <v>922667</v>
+        <v>900000</v>
       </c>
       <c r="F13">
-        <v>280000</v>
+        <v>296437</v>
       </c>
       <c r="G13">
-        <v>3281250</v>
+        <v>3215101</v>
       </c>
       <c r="H13">
-        <v>2771</v>
+        <v>11207</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B14">
-        <v>2018</v>
+        <v>2023</v>
       </c>
       <c r="C14">
-        <v>1230311</v>
+        <v>1607004</v>
       </c>
       <c r="D14">
-        <v>1641667</v>
+        <v>2486557</v>
       </c>
       <c r="E14">
-        <v>785000</v>
+        <v>986756</v>
       </c>
       <c r="F14">
-        <v>272280</v>
+        <v>301250</v>
       </c>
       <c r="G14">
-        <v>2505772</v>
+        <v>3360423</v>
       </c>
       <c r="H14">
-        <v>12783</v>
+        <v>10841</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Medellín</t>
+          <t>Cali</t>
         </is>
       </c>
       <c r="B15">
-        <v>2019</v>
+        <v>2024</v>
       </c>
       <c r="C15">
-        <v>1272180</v>
+        <v>1722746</v>
       </c>
       <c r="D15">
-        <v>1601743</v>
+        <v>2405823</v>
       </c>
       <c r="E15">
-        <v>808333</v>
+        <v>1038333</v>
       </c>
       <c r="F15">
-        <v>275000</v>
+        <v>322500</v>
       </c>
       <c r="G15">
-        <v>2674206</v>
+        <v>3625000</v>
       </c>
       <c r="H15">
-        <v>12934</v>
+        <v>10548</v>
       </c>
     </row>
     <row r="16">
@@ -796,25 +796,25 @@
         </is>
       </c>
       <c r="B16">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="C16">
-        <v>1201340</v>
+        <v>1230311</v>
       </c>
       <c r="D16">
-        <v>1676668</v>
+        <v>1641667</v>
       </c>
       <c r="E16">
-        <v>731097</v>
+        <v>785000</v>
       </c>
       <c r="F16">
-        <v>175000</v>
+        <v>272280</v>
       </c>
       <c r="G16">
-        <v>2612500</v>
+        <v>2505772</v>
       </c>
       <c r="H16">
-        <v>12714</v>
+        <v>12783</v>
       </c>
     </row>
     <row r="17">
@@ -824,25 +824,25 @@
         </is>
       </c>
       <c r="B17">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="C17">
-        <v>1359713</v>
+        <v>1272180</v>
       </c>
       <c r="D17">
-        <v>1744536</v>
+        <v>1601743</v>
       </c>
       <c r="E17">
-        <v>860000</v>
+        <v>808333</v>
       </c>
       <c r="F17">
-        <v>263739</v>
+        <v>275000</v>
       </c>
       <c r="G17">
-        <v>2874234</v>
+        <v>2674206</v>
       </c>
       <c r="H17">
-        <v>12697</v>
+        <v>12934</v>
       </c>
     </row>
     <row r="18">
@@ -852,25 +852,25 @@
         </is>
       </c>
       <c r="B18">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="C18">
-        <v>1714928</v>
+        <v>1201340</v>
       </c>
       <c r="D18">
-        <v>2436743</v>
+        <v>1676668</v>
       </c>
       <c r="E18">
-        <v>1039086</v>
+        <v>731097</v>
       </c>
       <c r="F18">
-        <v>331803</v>
+        <v>175000</v>
       </c>
       <c r="G18">
-        <v>3583333</v>
+        <v>2612500</v>
       </c>
       <c r="H18">
-        <v>12215</v>
+        <v>12714</v>
       </c>
     </row>
     <row r="19">
@@ -880,25 +880,109 @@
         </is>
       </c>
       <c r="B19">
+        <v>2021</v>
+      </c>
+      <c r="C19">
+        <v>1359713</v>
+      </c>
+      <c r="D19">
+        <v>1744536</v>
+      </c>
+      <c r="E19">
+        <v>860000</v>
+      </c>
+      <c r="F19">
+        <v>263739</v>
+      </c>
+      <c r="G19">
+        <v>2874234</v>
+      </c>
+      <c r="H19">
+        <v>12697</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B20">
+        <v>2022</v>
+      </c>
+      <c r="C20">
+        <v>1714928</v>
+      </c>
+      <c r="D20">
+        <v>2436743</v>
+      </c>
+      <c r="E20">
+        <v>1039086</v>
+      </c>
+      <c r="F20">
+        <v>331803</v>
+      </c>
+      <c r="G20">
+        <v>3583333</v>
+      </c>
+      <c r="H20">
+        <v>12215</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B21">
         <v>2023</v>
       </c>
-      <c r="C19">
-        <v>1740304</v>
-      </c>
-      <c r="D19">
-        <v>2833256</v>
-      </c>
-      <c r="E19">
-        <v>1071167</v>
-      </c>
-      <c r="F19">
-        <v>300126</v>
-      </c>
-      <c r="G19">
-        <v>3820833</v>
-      </c>
-      <c r="H19">
-        <v>2291</v>
+      <c r="C21">
+        <v>1918763</v>
+      </c>
+      <c r="D21">
+        <v>2359815</v>
+      </c>
+      <c r="E21">
+        <v>1231667</v>
+      </c>
+      <c r="F21">
+        <v>380000</v>
+      </c>
+      <c r="G21">
+        <v>4197465</v>
+      </c>
+      <c r="H21">
+        <v>11994</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="B22">
+        <v>2024</v>
+      </c>
+      <c r="C22">
+        <v>2217220</v>
+      </c>
+      <c r="D22">
+        <v>2935946</v>
+      </c>
+      <c r="E22">
+        <v>1436667</v>
+      </c>
+      <c r="F22">
+        <v>450000</v>
+      </c>
+      <c r="G22">
+        <v>4640089</v>
+      </c>
+      <c r="H22">
+        <v>11849</v>
       </c>
     </row>
   </sheetData>
@@ -908,7 +992,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -952,6 +1036,11 @@
           <t>2023</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -980,7 +1069,10 @@
         <v>2006406</v>
       </c>
       <c r="H2">
-        <v>2155699</v>
+        <v>2312956</v>
+      </c>
+      <c r="I2">
+        <v>2603861</v>
       </c>
     </row>
     <row r="3">
@@ -1010,7 +1102,10 @@
         <v>2998648</v>
       </c>
       <c r="H3">
-        <v>3038656</v>
+        <v>3189610</v>
+      </c>
+      <c r="I3">
+        <v>3643506</v>
       </c>
     </row>
     <row r="4">
@@ -1040,7 +1135,10 @@
         <v>1100000</v>
       </c>
       <c r="H4">
-        <v>1201923</v>
+        <v>1320833</v>
+      </c>
+      <c r="I4">
+        <v>1512400</v>
       </c>
     </row>
     <row r="5">
@@ -1070,7 +1168,10 @@
         <v>300595</v>
       </c>
       <c r="H5">
-        <v>331500</v>
+        <v>391389</v>
+      </c>
+      <c r="I5">
+        <v>484444</v>
       </c>
     </row>
     <row r="6">
@@ -1100,7 +1201,10 @@
         <v>4596717</v>
       </c>
       <c r="H6">
-        <v>4867917</v>
+        <v>5150000</v>
+      </c>
+      <c r="I6">
+        <v>5735167</v>
       </c>
     </row>
     <row r="7">
@@ -1130,7 +1234,10 @@
         <v>1505300</v>
       </c>
       <c r="H7">
-        <v>1586549</v>
+        <v>1607004</v>
+      </c>
+      <c r="I7">
+        <v>1722746</v>
       </c>
     </row>
     <row r="8">
@@ -1160,7 +1267,10 @@
         <v>2141240</v>
       </c>
       <c r="H8">
-        <v>3285389</v>
+        <v>2486557</v>
+      </c>
+      <c r="I8">
+        <v>2405823</v>
       </c>
     </row>
     <row r="9">
@@ -1190,7 +1300,10 @@
         <v>900000</v>
       </c>
       <c r="H9">
-        <v>922667</v>
+        <v>986756</v>
+      </c>
+      <c r="I9">
+        <v>1038333</v>
       </c>
     </row>
     <row r="10">
@@ -1220,7 +1333,10 @@
         <v>296437</v>
       </c>
       <c r="H10">
-        <v>280000</v>
+        <v>301250</v>
+      </c>
+      <c r="I10">
+        <v>322500</v>
       </c>
     </row>
     <row r="11">
@@ -1250,7 +1366,10 @@
         <v>3215101</v>
       </c>
       <c r="H11">
-        <v>3281250</v>
+        <v>3360423</v>
+      </c>
+      <c r="I11">
+        <v>3625000</v>
       </c>
     </row>
     <row r="12">
@@ -1280,7 +1399,10 @@
         <v>1714928</v>
       </c>
       <c r="H12">
-        <v>1740304</v>
+        <v>1918763</v>
+      </c>
+      <c r="I12">
+        <v>2217220</v>
       </c>
     </row>
     <row r="13">
@@ -1310,7 +1432,10 @@
         <v>2436743</v>
       </c>
       <c r="H13">
-        <v>2833256</v>
+        <v>2359815</v>
+      </c>
+      <c r="I13">
+        <v>2935946</v>
       </c>
     </row>
     <row r="14">
@@ -1340,7 +1465,10 @@
         <v>1039086</v>
       </c>
       <c r="H14">
-        <v>1071167</v>
+        <v>1231667</v>
+      </c>
+      <c r="I14">
+        <v>1436667</v>
       </c>
     </row>
     <row r="15">
@@ -1370,7 +1498,10 @@
         <v>331803</v>
       </c>
       <c r="H15">
-        <v>300126</v>
+        <v>380000</v>
+      </c>
+      <c r="I15">
+        <v>450000</v>
       </c>
     </row>
     <row r="16">
@@ -1400,7 +1531,10 @@
         <v>3583333</v>
       </c>
       <c r="H16">
-        <v>3820833</v>
+        <v>4197465</v>
+      </c>
+      <c r="I16">
+        <v>4640089</v>
       </c>
     </row>
   </sheetData>
